--- a/demo_data/vitals.xlsx
+++ b/demo_data/vitals.xlsx
@@ -481,37 +481,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UHID-1006</t>
+          <t>UHID-1003</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-14 02:11</t>
+          <t>2026-06-14 10:26</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="E2" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="G2" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H2" t="n">
-        <v>36</v>
+        <v>37.7</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J2" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="K2" t="n">
-        <v>4261</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="3">
@@ -522,37 +522,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UHID-1015</t>
+          <t>UHID-1010</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-13 12:11</t>
+          <t>2026-06-13 22:26</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="E3" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="G3" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H3" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="I3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J3" t="n">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="K3" t="n">
-        <v>6237</v>
+        <v>7712</v>
       </c>
     </row>
     <row r="4">
@@ -563,37 +563,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UHID-1010</t>
+          <t>UHID-1003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-13 20:11</t>
+          <t>2026-06-13 17:26</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="G4" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H4" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
       <c r="I4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K4" t="n">
-        <v>1740</v>
+        <v>9098</v>
       </c>
     </row>
     <row r="5">
@@ -604,37 +604,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UHID-1009</t>
+          <t>UHID-1000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-13 04:11</t>
+          <t>2026-06-12 02:26</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E5" t="n">
         <v>71</v>
       </c>
       <c r="F5" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="G5" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H5" t="n">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="I5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="K5" t="n">
-        <v>11157</v>
+        <v>6807</v>
       </c>
     </row>
     <row r="6">
@@ -650,32 +650,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-13 19:11</t>
+          <t>2026-06-14 02:26</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H6" t="n">
-        <v>37.3</v>
+        <v>36.7</v>
       </c>
       <c r="I6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J6" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="K6" t="n">
-        <v>9734</v>
+        <v>5167</v>
       </c>
     </row>
     <row r="7">
@@ -686,37 +686,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UHID-1012</t>
+          <t>UHID-1000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-13 09:11</t>
+          <t>2026-06-13 08:26</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="F7" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G7" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H7" t="n">
-        <v>36</v>
+        <v>37.2</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J7" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="K7" t="n">
-        <v>6395</v>
+        <v>10878</v>
       </c>
     </row>
     <row r="8">
@@ -727,37 +727,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UHID-1010</t>
+          <t>UHID-1008</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-11 15:11</t>
+          <t>2026-06-12 04:26</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E8" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F8" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>37.2</v>
+        <v>38.1</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J8" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="K8" t="n">
-        <v>1654</v>
+        <v>11239</v>
       </c>
     </row>
     <row r="9">
@@ -768,37 +768,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UHID-1003</t>
+          <t>UHID-1011</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-06-12 01:11</t>
+          <t>2026-06-13 09:26</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="E9" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F9" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="G9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H9" t="n">
-        <v>36.5</v>
+        <v>36.7</v>
       </c>
       <c r="I9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J9" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K9" t="n">
-        <v>10217</v>
+        <v>8809</v>
       </c>
     </row>
     <row r="10">
@@ -809,37 +809,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UHID-1003</t>
+          <t>UHID-1008</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-06-12 01:11</t>
+          <t>2026-06-13 03:26</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="F10" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="G10" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H10" t="n">
-        <v>36.8</v>
+        <v>37.8</v>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="K10" t="n">
-        <v>4482</v>
+        <v>8020</v>
       </c>
     </row>
     <row r="11">
@@ -850,37 +850,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UHID-1000</t>
+          <t>UHID-1006</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-12 20:11</t>
+          <t>2026-06-14 16:26</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F11" t="n">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="G11" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H11" t="n">
         <v>37.7</v>
       </c>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J11" t="n">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K11" t="n">
-        <v>10592</v>
+        <v>6883</v>
       </c>
     </row>
     <row r="12">
@@ -891,37 +891,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UHID-1006</t>
+          <t>UHID-1009</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-12 03:11</t>
+          <t>2026-06-14 06:26</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="E12" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="F12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H12" t="n">
-        <v>37.9</v>
+        <v>36</v>
       </c>
       <c r="I12" t="n">
         <v>21</v>
       </c>
       <c r="J12" t="n">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="K12" t="n">
-        <v>6979</v>
+        <v>5065</v>
       </c>
     </row>
     <row r="13">
@@ -932,37 +932,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UHID-1002</t>
+          <t>UHID-1008</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-12 13:11</t>
+          <t>2026-06-14 01:26</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="E13" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F13" t="n">
+        <v>72</v>
+      </c>
+      <c r="G13" t="n">
         <v>92</v>
       </c>
-      <c r="G13" t="n">
-        <v>98</v>
-      </c>
       <c r="H13" t="n">
-        <v>37.3</v>
+        <v>36.4</v>
       </c>
       <c r="I13" t="n">
         <v>16</v>
       </c>
       <c r="J13" t="n">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="K13" t="n">
-        <v>5375</v>
+        <v>9737</v>
       </c>
     </row>
     <row r="14">
@@ -973,37 +973,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UHID-1017</t>
+          <t>UHID-1011</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-14 06:11</t>
+          <t>2026-06-12 19:26</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="E14" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F14" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="G14" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H14" t="n">
-        <v>36.5</v>
+        <v>37.9</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="K14" t="n">
-        <v>6058</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="15">
@@ -1014,37 +1014,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UHID-1005</t>
+          <t>UHID-1002</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-13 22:11</t>
+          <t>2026-06-11 16:26</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F15" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G15" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H15" t="n">
-        <v>37.3</v>
+        <v>36.5</v>
       </c>
       <c r="I15" t="n">
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="K15" t="n">
-        <v>11390</v>
+        <v>4326</v>
       </c>
     </row>
     <row r="16">
@@ -1055,37 +1055,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UHID-1018</t>
+          <t>UHID-1014</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-13 20:11</t>
+          <t>2026-06-14 00:26</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="F16" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="G16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H16" t="n">
-        <v>37.8</v>
+        <v>37.2</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="K16" t="n">
-        <v>10395</v>
+        <v>9640</v>
       </c>
     </row>
     <row r="17">
@@ -1096,37 +1096,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UHID-1003</t>
+          <t>UHID-1013</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-13 14:11</t>
+          <t>2026-06-14 16:26</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="E17" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="F17" t="n">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="G17" t="n">
         <v>96</v>
       </c>
       <c r="H17" t="n">
-        <v>38.5</v>
+        <v>36.1</v>
       </c>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="K17" t="n">
-        <v>5120</v>
+        <v>7855</v>
       </c>
     </row>
     <row r="18">
@@ -1137,37 +1137,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UHID-1016</t>
+          <t>UHID-1008</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-12 23:11</t>
+          <t>2026-06-13 19:26</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="E18" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F18" t="n">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="G18" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H18" t="n">
-        <v>37.6</v>
+        <v>37.9</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K18" t="n">
-        <v>1723</v>
+        <v>9643</v>
       </c>
     </row>
     <row r="19">
@@ -1178,37 +1178,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UHID-1003</t>
+          <t>UHID-1018</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-06-11 23:11</t>
+          <t>2026-06-12 20:26</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E19" t="n">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="F19" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G19" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H19" t="n">
-        <v>37.3</v>
+        <v>36.5</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="K19" t="n">
-        <v>11195</v>
+        <v>4985</v>
       </c>
     </row>
     <row r="20">
@@ -1219,37 +1219,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UHID-1012</t>
+          <t>UHID-1013</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-06-14 04:11</t>
+          <t>2026-06-14 07:26</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E20" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="F20" t="n">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="G20" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H20" t="n">
-        <v>37.4</v>
+        <v>38.3</v>
       </c>
       <c r="I20" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="K20" t="n">
-        <v>3250</v>
+        <v>6525</v>
       </c>
     </row>
     <row r="21">
@@ -1260,37 +1260,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UHID-1015</t>
+          <t>UHID-1006</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-06-13 22:11</t>
+          <t>2026-06-11 21:26</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="E21" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F21" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="G21" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H21" t="n">
-        <v>37.3</v>
+        <v>37.9</v>
       </c>
       <c r="I21" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K21" t="n">
-        <v>2476</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="22">
@@ -1301,37 +1301,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UHID-1009</t>
+          <t>UHID-1016</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-06-14 11:11</t>
+          <t>2026-06-14 14:26</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="E22" t="n">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="F22" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="G22" t="n">
         <v>99</v>
       </c>
       <c r="H22" t="n">
-        <v>36.3</v>
+        <v>36.9</v>
       </c>
       <c r="I22" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="K22" t="n">
-        <v>2425</v>
+        <v>5298</v>
       </c>
     </row>
     <row r="23">
@@ -1342,37 +1342,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UHID-1017</t>
+          <t>UHID-1006</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-06-14 05:11</t>
+          <t>2026-06-12 13:26</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="E23" t="n">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="F23" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G23" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H23" t="n">
-        <v>37.2</v>
+        <v>36.9</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="K23" t="n">
-        <v>7592</v>
+        <v>8621</v>
       </c>
     </row>
     <row r="24">
@@ -1383,37 +1383,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UHID-1002</t>
+          <t>UHID-1019</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-06-14 03:11</t>
+          <t>2026-06-13 11:26</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="E24" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F24" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="G24" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H24" t="n">
-        <v>37.4</v>
+        <v>36.7</v>
       </c>
       <c r="I24" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="K24" t="n">
-        <v>8296</v>
+        <v>8059</v>
       </c>
     </row>
     <row r="25">
@@ -1424,37 +1424,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UHID-1015</t>
+          <t>UHID-1008</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-06-13 16:11</t>
+          <t>2026-06-14 00:26</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="E25" t="n">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F25" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="G25" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H25" t="n">
-        <v>36.1</v>
+        <v>37.5</v>
       </c>
       <c r="I25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="K25" t="n">
-        <v>9595</v>
+        <v>3690</v>
       </c>
     </row>
     <row r="26">
@@ -1465,37 +1465,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UHID-1012</t>
+          <t>UHID-1002</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-06-14 09:11</t>
+          <t>2026-06-13 17:26</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="E26" t="n">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="F26" t="n">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="G26" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>36.3</v>
+        <v>36.6</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J26" t="n">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="K26" t="n">
-        <v>9666</v>
+        <v>5786</v>
       </c>
     </row>
     <row r="27">
@@ -1506,37 +1506,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UHID-1010</t>
+          <t>UHID-1002</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-06-12 10:11</t>
+          <t>2026-06-13 06:26</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E27" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="F27" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G27" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H27" t="n">
-        <v>37.4</v>
+        <v>36.6</v>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="K27" t="n">
-        <v>6983</v>
+        <v>6689</v>
       </c>
     </row>
     <row r="28">
@@ -1547,37 +1547,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UHID-1016</t>
+          <t>UHID-1006</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-06-12 21:11</t>
+          <t>2026-06-13 04:26</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="E28" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F28" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="G28" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H28" t="n">
-        <v>38.4</v>
+        <v>37.6</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J28" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="K28" t="n">
-        <v>1005</v>
+        <v>4338</v>
       </c>
     </row>
     <row r="29">
@@ -1588,37 +1588,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UHID-1019</t>
+          <t>UHID-1002</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-06-12 21:11</t>
+          <t>2026-06-11 19:26</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="E29" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F29" t="n">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="G29" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H29" t="n">
-        <v>36.5</v>
+        <v>38.5</v>
       </c>
       <c r="I29" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="K29" t="n">
-        <v>8177</v>
+        <v>4552</v>
       </c>
     </row>
     <row r="30">
@@ -1629,37 +1629,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UHID-1013</t>
+          <t>UHID-1008</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-06-11 21:11</t>
+          <t>2026-06-14 13:26</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="E30" t="n">
         <v>72</v>
       </c>
       <c r="F30" t="n">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="G30" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H30" t="n">
         <v>37.7</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J30" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="K30" t="n">
-        <v>5348</v>
+        <v>10754</v>
       </c>
     </row>
     <row r="31">
@@ -1670,37 +1670,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UHID-1004</t>
+          <t>UHID-1011</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-06-12 04:11</t>
+          <t>2026-06-13 16:26</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="E31" t="n">
         <v>79</v>
       </c>
       <c r="F31" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="G31" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H31" t="n">
-        <v>36</v>
+        <v>37.7</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="K31" t="n">
-        <v>11786</v>
+        <v>11214</v>
       </c>
     </row>
   </sheetData>
